--- a/[포트폴리오] 맵.xlsx
+++ b/[포트폴리오] 맵.xlsx
@@ -1,112 +1,536 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
-  <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
-  </bookViews>
-  <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-  </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
-</workbook>
+<x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:fileVersion appName="HCell" lastEdited="12.0" lowestEdited="12.0" rupBuild="0.3650"/>
+  <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\82103\OneDrive\바탕 화면\Gihoek_5\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <x:bookViews>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="16710" windowHeight="8640"/>
+  </x:bookViews>
+  <x:sheets>
+    <x:sheet name="Sheet1" sheetId="1" r:id="rId3"/>
+  </x:sheets>
+  <x:calcPr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" mc:Ignorable="hs" hs:hclCalcId="904"/>
+</x:workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-  </fonts>
-  <fills count="2">
-    <fill>
-      <patternFill patternType="none"/>
-    </fill>
-    <fill>
-      <patternFill patternType="gray125"/>
-    </fill>
-  </fills>
-  <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-  </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-  </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-  </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-  </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
-</styleSheet>
+<x:styleSheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:fonts count="6">
+    <x:font>
+      <x:name val="맑은 고딕"/>
+      <x:sz val="11"/>
+      <x:color rgb="ff000000"/>
+    </x:font>
+    <x:font>
+      <x:name val="맑은 고딕"/>
+      <x:sz val="11"/>
+      <x:color rgb="ff000000"/>
+    </x:font>
+    <x:font>
+      <x:name val="맑은 고딕"/>
+      <x:sz val="11"/>
+      <x:color rgb="ff000000"/>
+    </x:font>
+    <x:font>
+      <x:name val="맑은 고딕"/>
+      <x:sz val="11"/>
+      <x:color rgb="ff000000"/>
+    </x:font>
+    <x:font>
+      <x:name val="맑은 고딕"/>
+      <x:sz val="11"/>
+      <x:color rgb="ff000000"/>
+    </x:font>
+    <x:font>
+      <x:name val="맑은 고딕"/>
+      <x:sz val="11"/>
+      <x:color rgb="ff000000"/>
+    </x:font>
+  </x:fonts>
+  <x:fills count="2">
+    <x:fill>
+      <x:patternFill patternType="none"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="gray125"/>
+    </x:fill>
+  </x:fills>
+  <x:borders count="1">
+    <x:border>
+      <x:left>
+        <x:color rgb="ff000000"/>
+      </x:left>
+      <x:right>
+        <x:color rgb="ff000000"/>
+      </x:right>
+      <x:top>
+        <x:color auto="1"/>
+      </x:top>
+      <x:bottom>
+        <x:color rgb="ff000000"/>
+      </x:bottom>
+    </x:border>
+  </x:borders>
+  <x:cellStyleXfs count="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+  </x:cellStyleXfs>
+  <x:cellXfs count="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <x:alignment horizontal="general" vertical="bottom"/>
+    </x:xf>
+  </x:cellXfs>
+  <x:cellStyles count="1">
+    <x:cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </x:cellStyles>
+  <x:dxfs count="12">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ffd7dff4"/>
+              <x:bgColor rgb="ffd7dff4"/>
+            </x:patternFill>
+          </x:fill>
+          <x:border>
+            <x:left style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:left>
+            <x:right style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:right>
+            <x:top style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:top>
+            <x:bottom style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:bottom>
+            <x:vertical style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:vertical>
+            <x:horizontal style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:horizontal>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ffd7dff4"/>
+              <x:bgColor rgb="ffd7dff4"/>
+            </x:patternFill>
+          </x:fill>
+          <x:border>
+            <x:left style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:left>
+            <x:right style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:right>
+            <x:top style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:top>
+            <x:bottom style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:bottom>
+            <x:vertical style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:vertical>
+            <x:horizontal style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:horizontal>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <x:dxf/>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ffaebfea"/>
+          <x:bgColor rgb="ffaebfea"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ffffffff"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ff6182d6"/>
+              <x:bgColor rgb="ff6182d6"/>
+            </x:patternFill>
+          </x:fill>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ffffffff"/>
+            <x:b val="1"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ff6182d6"/>
+              <x:bgColor rgb="ff6182d6"/>
+            </x:patternFill>
+          </x:fill>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ffffffff"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ff6182d6"/>
+              <x:bgColor rgb="ff6182d6"/>
+            </x:patternFill>
+          </x:fill>
+          <x:border>
+            <x:top style="thick">
+              <x:color rgb="ffffffff"/>
+            </x:top>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ffffffff"/>
+            <x:b val="1"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ff6182d6"/>
+              <x:bgColor rgb="ff6182d6"/>
+            </x:patternFill>
+          </x:fill>
+          <x:border>
+            <x:top style="thick">
+              <x:color rgb="ffffffff"/>
+            </x:top>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ffffffff"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ff6182d6"/>
+              <x:bgColor rgb="ff6182d6"/>
+            </x:patternFill>
+          </x:fill>
+          <x:border>
+            <x:bottom style="thick">
+              <x:color rgb="ffffffff"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ffffffff"/>
+            <x:b val="1"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ff6182d6"/>
+              <x:bgColor rgb="ff6182d6"/>
+            </x:patternFill>
+          </x:fill>
+          <x:border>
+            <x:bottom style="thick">
+              <x:color rgb="ffffffff"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:border>
+            <x:left>
+              <x:color auto="1"/>
+            </x:left>
+            <x:right>
+              <x:color auto="1"/>
+            </x:right>
+            <x:top style="medium">
+              <x:color rgb="ff6182d6"/>
+            </x:top>
+            <x:bottom style="medium">
+              <x:color rgb="ff6182d6"/>
+            </x:bottom>
+            <x:vertical>
+              <x:color auto="1"/>
+            </x:vertical>
+            <x:horizontal>
+              <x:color auto="1"/>
+            </x:horizontal>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+          </x:font>
+          <x:border>
+            <x:left>
+              <x:color auto="1"/>
+            </x:left>
+            <x:right>
+              <x:color auto="1"/>
+            </x:right>
+            <x:top style="medium">
+              <x:color rgb="ff6182d6"/>
+            </x:top>
+            <x:bottom style="medium">
+              <x:color rgb="ff6182d6"/>
+            </x:bottom>
+            <x:vertical>
+              <x:color auto="1"/>
+            </x:vertical>
+            <x:horizontal>
+              <x:color auto="1"/>
+            </x:horizontal>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ff94a5df"/>
+          <x:bgColor rgb="ff94a5df"/>
+        </x:patternFill>
+      </x:fill>
+      <x:border>
+        <x:top style="thin">
+          <x:color rgb="ff6182d6"/>
+        </x:top>
+        <x:bottom style="thin">
+          <x:color rgb="ff6182d6"/>
+        </x:bottom>
+      </x:border>
+    </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ff6182d6"/>
+          <x:bgColor rgb="ff6182d6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:b val="1"/>
+          </x:font>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:border>
+            <x:top style="thin">
+              <x:color rgb="ff6182d6"/>
+            </x:top>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:b val="1"/>
+          </x:font>
+          <x:border>
+            <x:top style="thin">
+              <x:color rgb="ff6182d6"/>
+            </x:top>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:border>
+            <x:bottom style="medium">
+              <x:color rgb="ff6182d6"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:b val="1"/>
+          </x:font>
+          <x:border>
+            <x:bottom style="medium">
+              <x:color rgb="ff6182d6"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+  </x:dxfs>
+  <x:tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <x:tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1" count="9">
+      <x:tableStyleElement type="wholeTable" size="1" dxfId="0"/>
+      <x:tableStyleElement type="headerRow" size="1" dxfId="5"/>
+      <x:tableStyleElement type="totalRow" size="1" dxfId="4"/>
+      <x:tableStyleElement type="firstColumn" size="1" dxfId="3"/>
+      <x:tableStyleElement type="lastColumn" size="1" dxfId="3"/>
+      <x:tableStyleElement type="firstRowStripe" size="1" dxfId="2"/>
+      <x:tableStyleElement type="secondRowStripe" size="1" dxfId="1"/>
+      <x:tableStyleElement type="firstColumnStripe" size="1" dxfId="2"/>
+      <x:tableStyleElement type="secondColumnStripe" size="1" dxfId="1"/>
+    </x:tableStyle>
+    <x:tableStyle name="Light Style 1 - Accent 1" pivot="1" table="0" count="8">
+      <x:tableStyleElement type="wholeTable" size="1" dxfId="6"/>
+      <x:tableStyleElement type="headerRow" size="1" dxfId="11"/>
+      <x:tableStyleElement type="totalRow" size="1" dxfId="10"/>
+      <x:tableStyleElement type="firstColumn" size="1" dxfId="9"/>
+      <x:tableStyleElement type="lastColumn" size="1" dxfId="9"/>
+      <x:tableStyleElement type="firstRowStripe" size="1" dxfId="7"/>
+      <x:tableStyleElement type="secondRowStripe" size="1" dxfId="1"/>
+      <x:tableStyleElement type="firstColumnStripe" size="1" dxfId="8"/>
+    </x:tableStyle>
+  </x:tableStyles>
+</x:styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:wp="http://schemas.openxmlformats.org/drawingml/2006/wordprocessingDrawing" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr val="window" lastClr="ffffff"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="44546a"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="e7e6e6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="5b9bd5"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="ed7d31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="a5a5a5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="ffc000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4472c4"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="70ad47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0563c1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="954f72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -245,21 +669,21 @@
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+          <a:miter/>
         </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+          <a:miter/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+          <a:miter/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -319,21 +743,16 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr codeName="Sheet1"/>
+  <x:dimension ref="A1:A1"/>
+  <x:sheetFormatPr defaultColWidth="9" defaultRowHeight="54" customHeight="1"/>
+  <x:sheetData/>
+  <x:pageMargins left="0.69999998807907104492" right="0.69999998807907104492" top="0.75" bottom="0.75" header="0.30000001192092895508" footer="0.30000001192092895508"/>
+  <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
+</x:worksheet>
 </file>